--- a/settings/data/Enemy.xlsx
+++ b/settings/data/Enemy.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectFiles\LOO\touhou_LOO-master\touhou_LOO-master\settings\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EC1054-7AC8-4670-A3BD-C28A8357412C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10055"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -27,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,9 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="68">
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
   </si>
   <si>
     <t>float</t>
@@ -53,7 +52,6 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -65,7 +63,6 @@
         <sz val="10"/>
         <color theme="4"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -75,14 +72,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">移动方式
 </t>
     </r>
@@ -91,7 +80,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -102,7 +90,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -114,7 +101,6 @@
         <sz val="10"/>
         <color theme="4"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -130,7 +116,6 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -142,7 +127,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -150,6 +134,22 @@
     </r>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">是否会被刷掉
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>敌人在屏幕外时是否可以被刷掉。</t>
+    </r>
+  </si>
+  <si>
     <t>基础体术伤害</t>
   </si>
   <si>
@@ -164,7 +164,6 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -176,7 +175,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -184,6 +182,52 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">无敌时间
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>从生成开始算起，敌人在这段时间（秒）内拥有100%的减伤。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">无敌衰减时间
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>从无敌时间结束开始，敌人的减伤会在这段时间（秒）内从100%线性衰减至0。</t>
+    </r>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -199,6 +243,9 @@
     <t>danmaku_creator</t>
   </si>
   <si>
+    <t>is_can_disappear</t>
+  </si>
+  <si>
     <t>physical_damage</t>
   </si>
   <si>
@@ -211,6 +258,12 @@
     <t>speed</t>
   </si>
   <si>
+    <t>invincibility_time</t>
+  </si>
+  <si>
+    <t>invincibility_decrease_time</t>
+  </si>
+  <si>
     <t>enm_memhappy</t>
   </si>
   <si>
@@ -326,13 +379,25 @@
   </si>
   <si>
     <t>慧音二符战船</t>
+  </si>
+  <si>
+    <t>enm_ufo</t>
+  </si>
+  <si>
+    <t>飞碟</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,7 +409,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -352,7 +416,164 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -360,43 +581,205 @@
       <sz val="10"/>
       <color theme="4"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -419,13 +802,279 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -447,25 +1096,75 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="d4c"/>
@@ -742,27 +1441,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="20.26953125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="11.90625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.453125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.90625" style="3" customWidth="1"/>
-    <col min="6" max="7" width="20.453125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7265625" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="20.2685185185185" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.2685185185185" customWidth="1"/>
+    <col min="3" max="3" width="11.9074074074074" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.4537037037037" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.9074074074074" style="3" customWidth="1"/>
+    <col min="6" max="8" width="20.4537037037037" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.7222222222222" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.1111111111111" style="3" customWidth="1"/>
+    <col min="12" max="12" width="32.2222222222222" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -782,534 +1483,749 @@
         <v>1</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="128.4" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="G4" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="G5" s="3">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>30</v>
+      </c>
+      <c r="J5" s="3">
+        <v>50</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="G6" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>45</v>
+      </c>
+      <c r="J6" s="3">
+        <v>50</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="125" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
         <v>3</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>30</v>
+      </c>
+      <c r="J7" s="3">
+        <v>150</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>30</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>30</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>30</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>30</v>
+      </c>
+      <c r="J11" s="3">
+        <v>100</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>30</v>
+      </c>
+      <c r="J12" s="3">
+        <v>100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>10</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J13" s="3">
+        <v>60</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>10</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>200</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3">
-        <v>5</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>45</v>
-      </c>
-      <c r="I6" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="3">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I13" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="3">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="str">
         <f>[1]d4c!$A$5</f>
         <v>dcrt_keine_ns1_2</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
         <v>5</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>30</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>1000</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="str">
         <f>[1]d4c!$A$6</f>
         <v>dcrt_keine_ns1_3</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>5</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="str">
         <f>[1]d4c!$A$9</f>
         <v>dcrt_keine_sc1_3</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>5</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="str">
         <f>[1]d4c!$A$10</f>
         <v>dcrt_keine_sc1_4</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
         <v>5</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>30</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>1000</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>5</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>250</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/settings/data/Enemy.xlsx
+++ b/settings/data/Enemy.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nep\Documents\touhou_survivors\settings\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A913D7AF-34AF-47A9-8BB1-AFEFDB21D625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10055"/>
+    <workbookView xWindow="1092" yWindow="1188" windowWidth="28308" windowHeight="15084" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -24,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -134,22 +143,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">是否会被刷掉
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>敌人在屏幕外时是否可以被刷掉。</t>
-    </r>
-  </si>
-  <si>
     <t>基础体术伤害</t>
   </si>
   <si>
@@ -182,14 +175,182 @@
     </r>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>movement</t>
+  </si>
+  <si>
+    <t>danmaku_creator</t>
+  </si>
+  <si>
+    <t>physical_damage</t>
+  </si>
+  <si>
+    <t>magical_damage</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>enm_memhappy</t>
+  </si>
+  <si>
+    <t>记忆幻影-快乐</t>
+  </si>
+  <si>
+    <t>zako</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>enm_memsad</t>
+  </si>
+  <si>
+    <t>记忆幻影-悲伤</t>
+  </si>
+  <si>
+    <t>enm_mempeace</t>
+  </si>
+  <si>
+    <t>记忆幻影-平淡</t>
+  </si>
+  <si>
+    <t>enm_kedama</t>
+  </si>
+  <si>
+    <t>毛玉</t>
+  </si>
+  <si>
+    <t>creep</t>
+  </si>
+  <si>
+    <t>enm_yuurei</t>
+  </si>
+  <si>
+    <t>幽灵</t>
+  </si>
+  <si>
+    <t>enm_onibi</t>
+  </si>
+  <si>
+    <t>鬼火</t>
+  </si>
+  <si>
+    <t>enm_book</t>
+  </si>
+  <si>
+    <t>书</t>
+  </si>
+  <si>
+    <t>enm_boy</t>
+  </si>
+  <si>
+    <t>男孩的记忆</t>
+  </si>
+  <si>
+    <t>enm_girl</t>
+  </si>
+  <si>
+    <t>女孩的记忆</t>
+  </si>
+  <si>
+    <t>enm_memcolorful</t>
+  </si>
+  <si>
+    <t>记忆幻影-多彩</t>
+  </si>
+  <si>
+    <t>elite</t>
+  </si>
+  <si>
+    <t>enm_eltkedama</t>
+  </si>
+  <si>
+    <t>精英毛玉</t>
+  </si>
+  <si>
+    <t>enm_teacher</t>
+  </si>
+  <si>
+    <t>教师的记忆</t>
+  </si>
+  <si>
+    <t>enm_keine_ns1_1</t>
+  </si>
+  <si>
+    <t>慧音一非使魔1</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>enm_keine_ns1_2</t>
+  </si>
+  <si>
+    <t>慧音一非使魔2</t>
+  </si>
+  <si>
+    <t>enm_keine_sc1_1</t>
+  </si>
+  <si>
+    <t>慧音一符使魔1</t>
+  </si>
+  <si>
+    <t>enm_keine_sc1_2</t>
+  </si>
+  <si>
+    <t>慧音一符使魔2</t>
+  </si>
+  <si>
+    <t>enm_keine_sc2</t>
+  </si>
+  <si>
+    <t>慧音二符战船</t>
+  </si>
+  <si>
+    <t>enm_ufo</t>
+  </si>
+  <si>
+    <t>飞碟</t>
+  </si>
+  <si>
+    <t>is_can_disappear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">是否会被刷掉
+</t>
+    </r>
     <r>
       <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="9"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>敌人在屏幕外时是否可以被刷掉。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>invincibility_time</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">无敌时间
 </t>
     </r>
@@ -203,16 +364,14 @@
       </rPr>
       <t>从生成开始算起，敌人在这段时间（秒）内拥有100%的减伤。</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>invincibility_decrease_time</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">无敌衰减时间
 </t>
     </r>
@@ -226,178 +385,14 @@
       </rPr>
       <t>从无敌时间结束开始，敌人的减伤会在这段时间（秒）内从100%线性衰减至0。</t>
     </r>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>danmaku_creator</t>
-  </si>
-  <si>
-    <t>is_can_disappear</t>
-  </si>
-  <si>
-    <t>physical_damage</t>
-  </si>
-  <si>
-    <t>magical_damage</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>invincibility_time</t>
-  </si>
-  <si>
-    <t>invincibility_decrease_time</t>
-  </si>
-  <si>
-    <t>enm_memhappy</t>
-  </si>
-  <si>
-    <t>记忆幻影-快乐</t>
-  </si>
-  <si>
-    <t>zako</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>enm_memsad</t>
-  </si>
-  <si>
-    <t>记忆幻影-悲伤</t>
-  </si>
-  <si>
-    <t>enm_mempeace</t>
-  </si>
-  <si>
-    <t>记忆幻影-平淡</t>
-  </si>
-  <si>
-    <t>enm_kedama</t>
-  </si>
-  <si>
-    <t>毛玉</t>
-  </si>
-  <si>
-    <t>creep</t>
-  </si>
-  <si>
-    <t>enm_yuurei</t>
-  </si>
-  <si>
-    <t>幽灵</t>
-  </si>
-  <si>
-    <t>enm_onibi</t>
-  </si>
-  <si>
-    <t>鬼火</t>
-  </si>
-  <si>
-    <t>enm_book</t>
-  </si>
-  <si>
-    <t>书</t>
-  </si>
-  <si>
-    <t>enm_boy</t>
-  </si>
-  <si>
-    <t>男孩的记忆</t>
-  </si>
-  <si>
-    <t>enm_girl</t>
-  </si>
-  <si>
-    <t>女孩的记忆</t>
-  </si>
-  <si>
-    <t>enm_memcolorful</t>
-  </si>
-  <si>
-    <t>记忆幻影-多彩</t>
-  </si>
-  <si>
-    <t>elite</t>
-  </si>
-  <si>
-    <t>enm_eltkedama</t>
-  </si>
-  <si>
-    <t>精英毛玉</t>
-  </si>
-  <si>
-    <t>enm_teacher</t>
-  </si>
-  <si>
-    <t>教师的记忆</t>
-  </si>
-  <si>
-    <t>enm_keine_ns1_1</t>
-  </si>
-  <si>
-    <t>慧音一非使魔1</t>
-  </si>
-  <si>
-    <t>static</t>
-  </si>
-  <si>
-    <t>enm_keine_ns1_2</t>
-  </si>
-  <si>
-    <t>慧音一非使魔2</t>
-  </si>
-  <si>
-    <t>enm_keine_sc1_1</t>
-  </si>
-  <si>
-    <t>慧音一符使魔1</t>
-  </si>
-  <si>
-    <t>enm_keine_sc1_2</t>
-  </si>
-  <si>
-    <t>慧音一符使魔2</t>
-  </si>
-  <si>
-    <t>enm_keine_sc2</t>
-  </si>
-  <si>
-    <t>慧音二符战船</t>
-  </si>
-  <si>
-    <t>enm_ufo</t>
-  </si>
-  <si>
-    <t>飞碟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,150 +412,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -584,202 +435,38 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -826,255 +513,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1096,75 +541,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="d4c"/>
@@ -1441,29 +848,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.2685185185185" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.2685185185185" customWidth="1"/>
-    <col min="3" max="3" width="11.9074074074074" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.4537037037037" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.9074074074074" style="3" customWidth="1"/>
-    <col min="6" max="8" width="20.4537037037037" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.44140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" style="3" customWidth="1"/>
+    <col min="6" max="8" width="20.44140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.7222222222222" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.1111111111111" style="3" customWidth="1"/>
-    <col min="12" max="12" width="32.2222222222222" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="32.21875" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="128.4" spans="1:12">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="128.4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1517,78 +924,78 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="K3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="F4" s="3" t="b">
         <v>1</v>
@@ -1612,18 +1019,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="b">
         <v>1</v>
@@ -1647,18 +1054,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="b">
         <v>1</v>
@@ -1682,18 +1089,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7" s="3" t="b">
         <v>1</v>
@@ -1717,18 +1124,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="b">
         <v>1</v>
@@ -1752,18 +1159,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3" t="b">
         <v>1</v>
@@ -1787,18 +1194,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="b">
         <v>1</v>
@@ -1822,18 +1229,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F11" s="3" t="b">
         <v>1</v>
@@ -1857,18 +1264,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F12" s="3" t="b">
         <v>1</v>
@@ -1892,18 +1299,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F13" s="3" t="b">
         <v>0</v>
@@ -1927,18 +1334,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F14" s="3" t="b">
         <v>0</v>
@@ -1962,18 +1369,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>0</v>
@@ -1997,18 +1404,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="str">
         <f>[1]d4c!$A$5</f>
@@ -2036,18 +1443,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="str">
         <f>[1]d4c!$A$6</f>
@@ -2075,18 +1482,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E18" s="3" t="str">
         <f>[1]d4c!$A$9</f>
@@ -2114,18 +1521,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="str">
         <f>[1]d4c!$A$10</f>
@@ -2153,18 +1560,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F20" s="3" t="b">
         <v>0</v>
@@ -2188,18 +1595,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F21" s="3" t="b">
         <v>0</v>
@@ -2224,8 +1631,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/settings/data/Enemy.xlsx
+++ b/settings/data/Enemy.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nep\Documents\touhou_survivors\settings\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A913D7AF-34AF-47A9-8BB1-AFEFDB21D625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1092" yWindow="1188" windowWidth="28308" windowHeight="15084" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10055"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -30,9 +24,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -81,6 +72,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">移动方式
 </t>
     </r>
@@ -143,6 +141,29 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">是否会被刷掉
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>敌人在屏幕外时是否可以被刷掉。</t>
+    </r>
+  </si>
+  <si>
     <t>基础体术伤害</t>
   </si>
   <si>
@@ -175,182 +196,14 @@
     </r>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>danmaku_creator</t>
-  </si>
-  <si>
-    <t>physical_damage</t>
-  </si>
-  <si>
-    <t>magical_damage</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>enm_memhappy</t>
-  </si>
-  <si>
-    <t>记忆幻影-快乐</t>
-  </si>
-  <si>
-    <t>zako</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>enm_memsad</t>
-  </si>
-  <si>
-    <t>记忆幻影-悲伤</t>
-  </si>
-  <si>
-    <t>enm_mempeace</t>
-  </si>
-  <si>
-    <t>记忆幻影-平淡</t>
-  </si>
-  <si>
-    <t>enm_kedama</t>
-  </si>
-  <si>
-    <t>毛玉</t>
-  </si>
-  <si>
-    <t>creep</t>
-  </si>
-  <si>
-    <t>enm_yuurei</t>
-  </si>
-  <si>
-    <t>幽灵</t>
-  </si>
-  <si>
-    <t>enm_onibi</t>
-  </si>
-  <si>
-    <t>鬼火</t>
-  </si>
-  <si>
-    <t>enm_book</t>
-  </si>
-  <si>
-    <t>书</t>
-  </si>
-  <si>
-    <t>enm_boy</t>
-  </si>
-  <si>
-    <t>男孩的记忆</t>
-  </si>
-  <si>
-    <t>enm_girl</t>
-  </si>
-  <si>
-    <t>女孩的记忆</t>
-  </si>
-  <si>
-    <t>enm_memcolorful</t>
-  </si>
-  <si>
-    <t>记忆幻影-多彩</t>
-  </si>
-  <si>
-    <t>elite</t>
-  </si>
-  <si>
-    <t>enm_eltkedama</t>
-  </si>
-  <si>
-    <t>精英毛玉</t>
-  </si>
-  <si>
-    <t>enm_teacher</t>
-  </si>
-  <si>
-    <t>教师的记忆</t>
-  </si>
-  <si>
-    <t>enm_keine_ns1_1</t>
-  </si>
-  <si>
-    <t>慧音一非使魔1</t>
-  </si>
-  <si>
-    <t>static</t>
-  </si>
-  <si>
-    <t>enm_keine_ns1_2</t>
-  </si>
-  <si>
-    <t>慧音一非使魔2</t>
-  </si>
-  <si>
-    <t>enm_keine_sc1_1</t>
-  </si>
-  <si>
-    <t>慧音一符使魔1</t>
-  </si>
-  <si>
-    <t>enm_keine_sc1_2</t>
-  </si>
-  <si>
-    <t>慧音一符使魔2</t>
-  </si>
-  <si>
-    <t>enm_keine_sc2</t>
-  </si>
-  <si>
-    <t>慧音二符战船</t>
-  </si>
-  <si>
-    <t>enm_ufo</t>
-  </si>
-  <si>
-    <t>飞碟</t>
-  </si>
-  <si>
-    <t>is_can_disappear</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">是否会被刷掉
-</t>
-    </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color theme="9"/>
+        <sz val="16"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>敌人在屏幕外时是否可以被刷掉。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>invincibility_time</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">无敌时间
 </t>
     </r>
@@ -364,14 +217,16 @@
       </rPr>
       <t>从生成开始算起，敌人在这段时间（秒）内拥有100%的减伤。</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>invincibility_decrease_time</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">无敌衰减时间
 </t>
     </r>
@@ -385,14 +240,178 @@
       </rPr>
       <t>从无敌时间结束开始，敌人的减伤会在这段时间（秒）内从100%线性衰减至0。</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>movement</t>
+  </si>
+  <si>
+    <t>danmaku_creator</t>
+  </si>
+  <si>
+    <t>is_can_disappear</t>
+  </si>
+  <si>
+    <t>physical_damage</t>
+  </si>
+  <si>
+    <t>magical_damage</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>invincibility_time</t>
+  </si>
+  <si>
+    <t>invincibility_decrease_time</t>
+  </si>
+  <si>
+    <t>enm_memhappy</t>
+  </si>
+  <si>
+    <t>记忆幻影-快乐</t>
+  </si>
+  <si>
+    <t>zako</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>enm_memsad</t>
+  </si>
+  <si>
+    <t>记忆幻影-悲伤</t>
+  </si>
+  <si>
+    <t>enm_mempeace</t>
+  </si>
+  <si>
+    <t>记忆幻影-平淡</t>
+  </si>
+  <si>
+    <t>enm_kedama</t>
+  </si>
+  <si>
+    <t>毛玉</t>
+  </si>
+  <si>
+    <t>creep</t>
+  </si>
+  <si>
+    <t>enm_yuurei</t>
+  </si>
+  <si>
+    <t>幽灵</t>
+  </si>
+  <si>
+    <t>enm_onibi</t>
+  </si>
+  <si>
+    <t>鬼火</t>
+  </si>
+  <si>
+    <t>enm_book</t>
+  </si>
+  <si>
+    <t>书</t>
+  </si>
+  <si>
+    <t>enm_boy</t>
+  </si>
+  <si>
+    <t>男孩的记忆</t>
+  </si>
+  <si>
+    <t>enm_girl</t>
+  </si>
+  <si>
+    <t>女孩的记忆</t>
+  </si>
+  <si>
+    <t>enm_memcolorful</t>
+  </si>
+  <si>
+    <t>记忆幻影-多彩</t>
+  </si>
+  <si>
+    <t>elite</t>
+  </si>
+  <si>
+    <t>enm_eltkedama</t>
+  </si>
+  <si>
+    <t>精英毛玉</t>
+  </si>
+  <si>
+    <t>enm_teacher</t>
+  </si>
+  <si>
+    <t>教师的记忆</t>
+  </si>
+  <si>
+    <t>enm_keine_ns1_1</t>
+  </si>
+  <si>
+    <t>慧音一非使魔1</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>enm_keine_ns1_2</t>
+  </si>
+  <si>
+    <t>慧音一非使魔2</t>
+  </si>
+  <si>
+    <t>enm_keine_sc1_1</t>
+  </si>
+  <si>
+    <t>慧音一符使魔1</t>
+  </si>
+  <si>
+    <t>enm_keine_sc1_2</t>
+  </si>
+  <si>
+    <t>慧音一符使魔2</t>
+  </si>
+  <si>
+    <t>enm_keine_sc2</t>
+  </si>
+  <si>
+    <t>慧音二符战船</t>
+  </si>
+  <si>
+    <t>enm_ufo</t>
+  </si>
+  <si>
+    <t>飞碟</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +434,171 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="9"/>
       <name val="宋体"/>
@@ -428,45 +612,202 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -513,9 +854,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -541,37 +1124,81 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="d4c"/>
@@ -848,29 +1475,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" style="3" customWidth="1"/>
-    <col min="6" max="8" width="20.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="11.8888888888889" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.4444444444444" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.8888888888889" style="3" customWidth="1"/>
+    <col min="6" max="8" width="20.4444444444444" style="3" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="32.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.6666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.1111111111111" style="3" customWidth="1"/>
+    <col min="12" max="12" width="32.2222222222222" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -908,7 +1535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="128.4" x14ac:dyDescent="0.25">
+    <row r="2" s="2" customFormat="1" ht="128.4" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -924,78 +1551,78 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>63</v>
+      <c r="F2" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>67</v>
+        <v>12</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>62</v>
+        <v>19</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>66</v>
+        <v>24</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="b">
         <v>1</v>
@@ -1019,18 +1646,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3" t="b">
         <v>1</v>
@@ -1054,18 +1681,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="b">
         <v>1</v>
@@ -1089,18 +1716,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3" t="b">
         <v>1</v>
@@ -1124,18 +1751,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F8" s="3" t="b">
         <v>1</v>
@@ -1159,18 +1786,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="b">
         <v>1</v>
@@ -1194,18 +1821,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="b">
         <v>1</v>
@@ -1229,18 +1856,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F11" s="3" t="b">
         <v>1</v>
@@ -1264,18 +1891,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="b">
         <v>1</v>
@@ -1299,18 +1926,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="b">
         <v>0</v>
@@ -1334,18 +1961,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="b">
         <v>0</v>
@@ -1369,18 +1996,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>0</v>
@@ -1404,18 +2031,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="str">
         <f>[1]d4c!$A$5</f>
@@ -1443,18 +2070,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="str">
         <f>[1]d4c!$A$6</f>
@@ -1482,18 +2109,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="str">
         <f>[1]d4c!$A$9</f>
@@ -1521,18 +2148,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E19" s="3" t="str">
         <f>[1]d4c!$A$10</f>
@@ -1560,18 +2187,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F20" s="3" t="b">
         <v>0</v>
@@ -1595,18 +2222,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3" t="b">
         <v>0</v>
@@ -1624,15 +2251,15 @@
         <v>0</v>
       </c>
       <c r="K21" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/settings/data/Enemy.xlsx
+++ b/settings/data/Enemy.xlsx
@@ -119,13 +119,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">生成发弹点
 </t>
     </r>
@@ -329,16 +322,16 @@
     <t>书</t>
   </si>
   <si>
-    <t>enm_boy</t>
-  </si>
-  <si>
-    <t>男孩的记忆</t>
-  </si>
-  <si>
-    <t>enm_girl</t>
-  </si>
-  <si>
-    <t>女孩的记忆</t>
+    <t>enm_kedama_boy</t>
+  </si>
+  <si>
+    <t>男学生毛玉</t>
+  </si>
+  <si>
+    <t>enm_kedama_girl</t>
+  </si>
+  <si>
+    <t>女学生毛玉</t>
   </si>
   <si>
     <t>enm_memcolorful</t>
@@ -350,16 +343,16 @@
     <t>elite</t>
   </si>
   <si>
-    <t>enm_eltkedama</t>
-  </si>
-  <si>
-    <t>精英毛玉</t>
-  </si>
-  <si>
-    <t>enm_teacher</t>
-  </si>
-  <si>
-    <t>教师的记忆</t>
+    <t>enm_kedama_teacher</t>
+  </si>
+  <si>
+    <t>教师毛玉</t>
+  </si>
+  <si>
+    <t>enm_book_highermath</t>
+  </si>
+  <si>
+    <t>高等数学书</t>
   </si>
   <si>
     <t>enm_keine_ns1_1</t>
@@ -411,7 +404,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,20 +421,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -593,13 +572,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -608,6 +580,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -972,137 +951,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1124,17 +1103,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1484,7 +1457,7 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="20.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="23.1111111111111" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="11.8888888888889" style="3" customWidth="1"/>
     <col min="4" max="4" width="32.4444444444444" style="3" customWidth="1"/>
@@ -1551,7 +1524,7 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1566,10 +1539,10 @@
       <c r="J2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1589,7 +1562,7 @@
       <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1604,10 +1577,10 @@
       <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1867,7 +1840,7 @@
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="b">
         <v>1</v>
@@ -1902,7 +1875,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F12" s="3" t="b">
         <v>1</v>
@@ -1972,7 +1945,7 @@
         <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="b">
         <v>0</v>
